--- a/backend/非機能要件_ポートフォリオ実装可否マッピング.xlsx
+++ b/backend/非機能要件_ポートフォリオ実装可否マッピング.xlsx
@@ -1476,12 +1476,12 @@
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>ユーザー確認: MFA・条件付きアクセスは未設定</t>
+          <t>Microsoft Entra管理センターで確認: 「セキュリティの既定値群」が既に有効(組織全体でMFA強制済み)。テナントの既定設定として最初から満たされていた</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>ユーザー確認: MFAは未設定・未実演</t>
+          <t>23と同様、セキュリティの既定値群により既にMFAが有効化・実演確認済み(2026-08-28)</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>ユーザー確認: Dataverse監査ログは未有効化</t>
+          <t>組織全体の監査(Web API)+テーブル単位の監査(Power Apps管理画面)を実際に有効化・API確認済み(2026-08-28)。IsAuditEnabledのWeb API更新は"Operation not supported"で失敗したため、テーブル単位はUIから設定</t>
         </is>
       </c>
     </row>

--- a/backend/非機能要件_ポートフォリオ実装可否マッピング.xlsx
+++ b/backend/非機能要件_ポートフォリオ実装可否マッピング.xlsx
@@ -876,12 +876,12 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>負荷テスト(JMeter等)は未実施</t>
+          <t>run_load_test.py(concurrent.futuresによる疑似10並列アクセス)で実施。100リクエスト全て成功、平均応答624ms、95パーセンタイル728ms(2026-08-28)</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>○</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>検索速度の負荷シミュレーションは未実施</t>
+          <t>同上の負荷テストで応答速度を実測(平均624ms)。ただし約300件規模でのテストであり、5,200件相当のデータ量での検証は別途必要</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>○</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>ユーザー確認: バックアップ復元は未実演</t>
+          <t>pac admin backup/list-backupsで手動バックアップの作成・存在確認に成功。pac admin restoreも実行し正しいエラーハンドリング(処理待ち)まで確認したが、バックアップの復元可能化に時間を要するため完全な復元完了までは実施していない(2026-08-28)</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>ユーザー確認: ポイントインタイム復元は未実演</t>
+          <t>pac admin listで環境Typeが"Developer"であることを確認。ポイントインタイム復元(継続的バックアップ)は本番相当(Production/Sandboxで容量割当てが必要)環境限定の機能のため、このDeveloper環境では利用不可であることを確認した(2026-08-28)</t>
         </is>
       </c>
     </row>

--- a/backend/非機能要件_ポートフォリオ実装可否マッピング.xlsx
+++ b/backend/非機能要件_ポートフォリオ実装可否マッピング.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>運用手順書は未作成(該当ファイルなし)</t>
+          <t>運用_障害対応手順書.docxとして作成済み。日常運用の定期点検を、本プロジェクトの検証スクリプト群(verify_schema.py等)を用いる形で具体化した</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>障害対応手順書・バックアップ復元の実演は未実施</t>
+          <t>運用_障害対応手順書.docxに障害対応フロー・インシデント記録フォーマットを記載。バックアップ復元は非機能要件#37で別途実演確認済み</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>障害対応・再発防止プロセスの文書化は未実施</t>
+          <t>運用_障害対応手順書.docxに障害対応・再発防止プロセスを記載。実例としてfix-pcf-webpack.pyのハーネス化(再発防止の自動化)を明記</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>総務省ガイドライン等を参考にした設計方針文書は未作成</t>
+          <t>セキュリティ設計方針書.docxとして作成済み。総務省ガイドラインの4分類(組織的/人的/物理的/技術的対策)に沿って、実際の実装状況を整理</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>インシデント対応手順書は未作成</t>
+          <t>運用_障害対応手順書.docxにインシデント記録フォーマットを記載</t>
         </is>
       </c>
     </row>
@@ -2196,12 +2196,12 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>テスト計画書・テストケースは未作成(該当ファイルなし)</t>
+          <t>テスト計画書_実施結果報告書.docxとして作成済み。17件のテストケースと実施結果を記録(架空ではなく本セッションで実際に発見・修正した不具合の記録)</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>デモ協力者立会いのテストは未実施</t>
+          <t>デモ協力者が必要なため未実施。友人等への依頼が別途必要</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>実施計画書・結果報告書は未作成</t>
+          <t>テスト計画書_実施結果報告書.docxが実施計画・結果報告を兼ねる</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>簡易マニュアル・説明会資料は未作成</t>
+          <t>簡易マニュアル.docxとして作成済み。ロール別の操作内容とよくあるトラブルを記載</t>
         </is>
       </c>
     </row>
